--- a/artfynd/A 18300-2024 artfynd.xlsx
+++ b/artfynd/A 18300-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,7 +1719,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106276461</v>
+        <v>106276458</v>
       </c>
       <c r="B11" t="n">
         <v>98520</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473019.6783508952</v>
+        <v>473020.6330038146</v>
       </c>
       <c r="R11" t="n">
-        <v>7001272.675570898</v>
+        <v>7001278.546738218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106276458</v>
+        <v>106276421</v>
       </c>
       <c r="B12" t="n">
         <v>98520</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473020.6330038146</v>
+        <v>473087.4434455324</v>
       </c>
       <c r="R12" t="n">
-        <v>7001278.546738218</v>
+        <v>7001307.386113047</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106276421</v>
+        <v>106276477</v>
       </c>
       <c r="B13" t="n">
         <v>98520</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473087.4434455324</v>
+        <v>472865.2746973983</v>
       </c>
       <c r="R13" t="n">
-        <v>7001307.386113047</v>
+        <v>7001491.486588016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106276477</v>
+        <v>106276417</v>
       </c>
       <c r="B14" t="n">
         <v>98520</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472865.2746973983</v>
+        <v>473074.5176041804</v>
       </c>
       <c r="R14" t="n">
-        <v>7001491.486588016</v>
+        <v>7001223.37667008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106276417</v>
+        <v>106276485</v>
       </c>
       <c r="B15" t="n">
         <v>98520</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473074.5176041804</v>
+        <v>472938.6692219665</v>
       </c>
       <c r="R15" t="n">
-        <v>7001223.37667008</v>
+        <v>7001441.580900322</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106276485</v>
+        <v>106276419</v>
       </c>
       <c r="B16" t="n">
         <v>98520</v>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472938.6692219665</v>
+        <v>473077.3512105561</v>
       </c>
       <c r="R16" t="n">
-        <v>7001441.580900322</v>
+        <v>7001237.37274313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106276419</v>
+        <v>106276445</v>
       </c>
       <c r="B17" t="n">
         <v>98520</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473077.3512105561</v>
+        <v>472734.7508435863</v>
       </c>
       <c r="R17" t="n">
-        <v>7001237.37274313</v>
+        <v>7001586.1895709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106276445</v>
+        <v>106276470</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
+        <v>98431</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472734.7508435863</v>
+        <v>472878.8625105175</v>
       </c>
       <c r="R18" t="n">
-        <v>7001586.1895709</v>
+        <v>7001491.824931792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,122 +2644,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>106276470</v>
-      </c>
-      <c r="B19" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Jämtland, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>472878.8625105175</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7001491.824931792</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
